--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855251</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427404</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119760</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119761</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119777</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427409</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427378</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855305</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119852</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,48 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124427404</v>
+        <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>80367</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854289</v>
+        <v>854371</v>
       </c>
       <c r="R4" t="n">
-        <v>7479238</v>
+        <v>7479005</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,51 +980,51 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427404</t>
+          <t>https://artportalen.se/Sighting/136019207</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134119760</v>
+        <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>80493</v>
+        <v>83292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854328</v>
+        <v>854362</v>
       </c>
       <c r="R5" t="n">
-        <v>7479069</v>
+        <v>7479028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,51 +1082,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119760</t>
+          <t>https://artportalen.se/Sighting/136019239</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134119761</v>
+        <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>80493</v>
+        <v>83292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>854332</v>
+        <v>854359</v>
       </c>
       <c r="R6" t="n">
-        <v>7479065</v>
+        <v>7479055</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,51 +1184,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119761</t>
+          <t>https://artportalen.se/Sighting/136019240</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134119777</v>
+        <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>80493</v>
+        <v>83292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>854404</v>
+        <v>854355</v>
       </c>
       <c r="R7" t="n">
-        <v>7478864</v>
+        <v>7479061</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,54 +1286,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119777</t>
+          <t>https://artportalen.se/Sighting/136019241</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124427409</v>
+        <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>80467</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>3277</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>854407</v>
+        <v>854377</v>
       </c>
       <c r="R8" t="n">
-        <v>7478920</v>
+        <v>7479000</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,54 +1388,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427409</t>
+          <t>https://artportalen.se/Sighting/136019225</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124427377</v>
+        <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>80468</v>
+        <v>92178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>3277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>854407</v>
+        <v>854386</v>
       </c>
       <c r="R9" t="n">
-        <v>7478920</v>
+        <v>7479019</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,54 +1490,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427377</t>
+          <t>https://artportalen.se/Sighting/136019227</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124427378</v>
+        <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>80468</v>
+        <v>92178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>3277</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854414</v>
+        <v>854382</v>
       </c>
       <c r="R10" t="n">
-        <v>7478861</v>
+        <v>7479028</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,54 +1592,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427378</t>
+          <t>https://artportalen.se/Sighting/136019228</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124855305</v>
+        <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>92178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>3277</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>854281</v>
+        <v>854374</v>
       </c>
       <c r="R11" t="n">
-        <v>7479174</v>
+        <v>7479029</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,51 +1694,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855305</t>
+          <t>https://artportalen.se/Sighting/136019229</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134119852</v>
+        <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>57153</v>
+        <v>92178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>3277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>854326</v>
+        <v>854375</v>
       </c>
       <c r="R12" t="n">
-        <v>7479083</v>
+        <v>7479021</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1772,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 grupper med fruktkroppar nära varandra</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1779,6 +1791,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1796,7 +1809,3146 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136019230</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136019238</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>854410</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7478891</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019238</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124427404</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>854289</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7479238</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427404</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134119760</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>854328</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7479069</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119760</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134119761</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>854332</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7479065</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119761</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134119777</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>854404</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7478864</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119777</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136019214</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>854350</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7479038</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019214</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136019215</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>854344</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7479046</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019215</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136019216</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>854339</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7479128</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019216</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124427409</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>854407</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7478920</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427409</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124427377</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>854407</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7478920</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427377</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124427378</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>854414</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7478861</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124427378</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136019224</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>854344</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7479046</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019224</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124855305</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>854281</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7479174</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855305</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136019209</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>854390</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7478982</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre födosök  i form av avbarkad klen gran 2-4 år gammal. .</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019209</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136019210</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>854383</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7478979</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran. Kan antas vara gjorda av tretåig hackspett då arten förekommer i området och andra födosök noterats i närheten.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019210</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136019211</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>854357</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7479039</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran. 2-3 år gammalt.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019211</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136019212</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>854353</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7479064</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran. Antagligen födosök vintertid.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019212</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134119852</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>854326</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7479083</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134119852</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136019237</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57158</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>854439</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7478865</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019237</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136019231</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>854370</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7479029</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019231</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136019232</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>854443</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7478887</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019232</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136019233</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>854407</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7478891</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019233</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136019234</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>854374</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7478990</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019234</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136019235</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>854386</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7479026</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019235</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136019236</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>854377</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7479027</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019236</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136019217</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>854379</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7479010</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019217</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136019219</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>854352</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7479021</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019219</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136019220</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>854363</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7479028</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019220</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136019221</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>854363</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7479038</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019221</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136019222</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>854342</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7479060</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019222</t>
         </is>
       </c>
     </row>
@@ -1813,6 +4965,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136019209</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>136019210</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>136019211</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136019212</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136019237</v>
       </c>
       <c r="B31" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136019209</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>136019210</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>136019211</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136019212</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136019237</v>
       </c>
       <c r="B31" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136019209</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>136019210</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>136019211</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136019212</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136019237</v>
       </c>
       <c r="B31" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136019209</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>136019210</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>136019211</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136019212</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136019237</v>
       </c>
       <c r="B31" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136019209</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>136019210</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>136019211</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136019212</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136019237</v>
       </c>
       <c r="B31" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>136019209</v>
       </c>
       <c r="B26" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>136019210</v>
       </c>
       <c r="B27" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>136019211</v>
       </c>
       <c r="B28" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>136019212</v>
       </c>
       <c r="B29" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136019237</v>
       </c>
       <c r="B31" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136019239</v>
       </c>
       <c r="B5" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136019240</v>
       </c>
       <c r="B6" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136019241</v>
       </c>
       <c r="B7" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136019238</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136019214</v>
       </c>
       <c r="B18" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136019215</v>
       </c>
       <c r="B19" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136019216</v>
       </c>
       <c r="B20" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136019224</v>
       </c>
       <c r="B24" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
